--- a/tests/fixtures/02_product_catalog/pattern-from-draft.xlsx
+++ b/tests/fixtures/02_product_catalog/pattern-from-draft.xlsx
@@ -26,12 +26,37 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE8D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0FFD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D0FF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +71,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,274 +445,318 @@
   </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>config:</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>read.direction</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>col_sku</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>col_qty</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>lbl:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>col_price</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>item.name</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>.+</t>
         </is>
       </c>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>item.sku</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>[A-Z]{3}[0-9]{3}</t>
         </is>
       </c>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>item.qty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>integer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>[1-9][0-9]*</t>
         </is>
       </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>var:</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>item.price</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>.*</t>
         </is>
       </c>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>START:</t>
         </is>
       </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>table:*</t>
         </is>
       </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>HEADER:1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>col_product</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>col_sku</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>col_qty</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>col_price</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="3" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>DATA:*</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>item.name</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>item.sku</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>item.qty</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>item.price</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
